--- a/docs/templates/mock_drive/2026001 — Rockland/quotes/2026001_QUOTE_22-Plumbing_PlombertInc_selected.xlsx
+++ b/docs/templates/mock_drive/2026001 — Rockland/quotes/2026001_QUOTE_22-Plumbing_PlombertInc_selected.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -448,7 +448,8 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,6 +501,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SOW_Item_Ref</t>
         </is>
       </c>
     </row>
@@ -524,6 +530,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -561,7 +568,12 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PEX-A; per SOW-025</t>
+          <t>PEX-A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SOW-025</t>
         </is>
       </c>
     </row>
@@ -601,7 +613,12 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Moen Adler; per SOW-026</t>
+          <t>Moen Adler</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SOW-026</t>
         </is>
       </c>
     </row>
@@ -641,7 +658,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>40-gal electric; per SOW-027</t>
+          <t>40-gal electric</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SOW-027</t>
         </is>
       </c>
     </row>
@@ -662,6 +684,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -734,7 +757,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Subcontractor quote. Grid-readable: Material Amount / Labour Amount / Total Amount. Only QI-* rows are real quote line items. Row 2 (Item_ID empty) is a parser-control section-total row that sets the current CSI division for all QI-* rows that follow. The final row (Item_ID='Pre-Tax Total', Description empty) is a parser-control row that the grid parser captures as grand_total, not a line item.</t>
+          <t>Subcontractor quote. Grid-readable: Material Amount / Labour Amount / Total Amount. Only QI-* rows are real quote line items. Row 2 (Item_ID empty) is a parser-control section-total row that sets the current CSI division for all QI-* rows that follow. The final row (Item_ID='Pre-Tax Total', Description empty) is a parser-control row that the grid parser captures as grand_total, not a line item. SOW_Item_Ref is the structural join key back to SOW_Items/Package_Lines (e.g. 'SOW-025') -- never parse it out of Notes text.</t>
         </is>
       </c>
     </row>
